--- a/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>ObservationalStudyProtocolVersion; Study;
@@ -390,7 +390,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchStudy.meta.versionId</t>

--- a/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
@@ -1596,17 +1596,17 @@
   <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.0234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.0234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.171875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="32.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1615,27 +1615,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="171.58203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.97265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="147.1015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="207.0625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="97.8125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="181.859375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="177.51953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="83.85546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="155.9140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
@@ -454,7 +454,7 @@
     <t>ResearchStudy.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -492,7 +492,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -550,7 +550,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -690,7 +690,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -778,7 +778,7 @@
     <t>研究の主な意図をコードします。 / Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -799,7 +799,7 @@
     <t>臨床試験におけるヒトの初期実験的使用から市場後の評価への治療の進行の段階のコード。 / Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-phase</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-phase|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.phaseCode</t>
@@ -859,7 +859,7 @@
     <t>状態または診断の識別。 / Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>StudyCondition.code</t>
@@ -936,7 +936,7 @@
     <t>このアーティファクトが使用することを目的としている国と地域。 / Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -968,7 +968,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Group)
+    <t xml:space="preserve">Reference(Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1025,7 +1025,7 @@
     <t>ResearchStudy.sponsor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>ResearchStudy.site</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>研究が時期尚早に終了した理由をコードします。 / Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -1273,7 +1273,7 @@
     <t>学習目標の種類をコードします。 / Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -1606,7 +1606,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="32.32421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="41.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1621,7 +1621,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="147.1015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-researchstudy.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
